--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -23,7 +23,6 @@
     <sheet name="Лист9" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -33,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="43">
   <si>
     <t>Motivatsion-qadriyatli mezon (M)</t>
   </si>
@@ -119,12 +118,6 @@
     <t>Toshkent 319-son</t>
   </si>
   <si>
-    <t>Jizzax 45-son</t>
-  </si>
-  <si>
-    <t>Jizzax 125-son</t>
-  </si>
-  <si>
     <t>Jami</t>
   </si>
   <si>
@@ -159,6 +152,15 @@
   </si>
   <si>
     <t>R (NG)</t>
+  </si>
+  <si>
+    <t>Namangan  45-son</t>
+  </si>
+  <si>
+    <t>Namangan 125-son</t>
+  </si>
+  <si>
+    <t>Namangan 45-son</t>
   </si>
 </sst>
 </file>
@@ -298,24 +300,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -336,6 +320,24 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -751,11 +753,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="305484784"/>
-        <c:axId val="305485328"/>
+        <c:axId val="-821227296"/>
+        <c:axId val="-821234368"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="305484784"/>
+        <c:axId val="-821227296"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -798,7 +800,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="305485328"/>
+        <c:crossAx val="-821234368"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -806,7 +808,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="305485328"/>
+        <c:axId val="-821234368"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -857,7 +859,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="305484784"/>
+        <c:crossAx val="-821227296"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -921,6 +923,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1021,6 +1024,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1114,11 +1118,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="305490224"/>
-        <c:axId val="305492400"/>
+        <c:axId val="-821226752"/>
+        <c:axId val="-821238720"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="305490224"/>
+        <c:axId val="-821226752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1161,7 +1165,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="305492400"/>
+        <c:crossAx val="-821238720"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1169,7 +1173,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="305492400"/>
+        <c:axId val="-821238720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1220,7 +1224,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="305490224"/>
+        <c:crossAx val="-821226752"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1352,6 +1356,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1532,6 +1537,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1706,6 +1712,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1829,11 +1836,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="354208112"/>
-        <c:axId val="354215728"/>
+        <c:axId val="-821230016"/>
+        <c:axId val="-821225664"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="354208112"/>
+        <c:axId val="-821230016"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1873,7 +1880,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="354215728"/>
+        <c:crossAx val="-821225664"/>
         <c:crosses val="autoZero"/>
         <c:auto val="0"/>
         <c:lblAlgn val="ctr"/>
@@ -1881,7 +1888,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="354215728"/>
+        <c:axId val="-821225664"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1932,7 +1939,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="354208112"/>
+        <c:crossAx val="-821230016"/>
         <c:crossesAt val="1"/>
         <c:crossBetween val="midCat"/>
       </c:valAx>
@@ -1946,6 +1953,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -2435,11 +2443,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="354209200"/>
-        <c:axId val="354218992"/>
+        <c:axId val="-821231648"/>
+        <c:axId val="-821232192"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="354209200"/>
+        <c:axId val="-821231648"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2482,7 +2490,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="354218992"/>
+        <c:crossAx val="-821232192"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -2490,7 +2498,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="354218992"/>
+        <c:axId val="-821232192"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -2541,7 +2549,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="354209200"/>
+        <c:crossAx val="-821231648"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -2856,7 +2864,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -2892,10 +2899,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan  45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -3147,7 +3154,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -3183,10 +3189,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan  45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -3235,11 +3241,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:gapWidth val="65"/>
-        <c:axId val="357945856"/>
-        <c:axId val="357946400"/>
+        <c:axId val="-649875632"/>
+        <c:axId val="-649878896"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="357945856"/>
+        <c:axId val="-649875632"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3279,7 +3285,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="357946400"/>
+        <c:crossAx val="-649878896"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3287,7 +3293,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="357946400"/>
+        <c:axId val="-649878896"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3323,7 +3329,7 @@
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
-        <c:crossAx val="357945856"/>
+        <c:crossAx val="-649875632"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -3524,10 +3530,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -3662,10 +3668,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -3715,11 +3721,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="565837984"/>
-        <c:axId val="565840160"/>
+        <c:axId val="-649878352"/>
+        <c:axId val="-649871824"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="565837984"/>
+        <c:axId val="-649878352"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3759,7 +3765,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565840160"/>
+        <c:crossAx val="-649871824"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3767,7 +3773,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="565840160"/>
+        <c:axId val="-649871824"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3815,7 +3821,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565837984"/>
+        <c:crossAx val="-649878352"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4018,10 +4024,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4158,10 +4164,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4211,11 +4217,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="571369664"/>
-        <c:axId val="571364768"/>
+        <c:axId val="-649876720"/>
+        <c:axId val="-649866928"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="571369664"/>
+        <c:axId val="-649876720"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4255,7 +4261,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571364768"/>
+        <c:crossAx val="-649866928"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4263,7 +4269,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="571364768"/>
+        <c:axId val="-649866928"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4311,7 +4317,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571369664"/>
+        <c:crossAx val="-649876720"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4514,10 +4520,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4654,10 +4660,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4707,11 +4713,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="565167536"/>
-        <c:axId val="565168080"/>
+        <c:axId val="-649871280"/>
+        <c:axId val="-649876176"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="565167536"/>
+        <c:axId val="-649871280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4751,7 +4757,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565168080"/>
+        <c:crossAx val="-649876176"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -4759,7 +4765,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="565168080"/>
+        <c:axId val="-649876176"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4807,7 +4813,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="565167536"/>
+        <c:crossAx val="-649871280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5281,7 +5287,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5371,7 +5377,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5554,11 +5560,11 @@
         </c:dLbls>
         <c:gapWidth val="219"/>
         <c:overlap val="-27"/>
-        <c:axId val="571363680"/>
-        <c:axId val="571370752"/>
+        <c:axId val="-649870736"/>
+        <c:axId val="-649864752"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="571363680"/>
+        <c:axId val="-649870736"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5598,7 +5604,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571370752"/>
+        <c:crossAx val="-649864752"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -5606,7 +5612,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="571370752"/>
+        <c:axId val="-649864752"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -5654,7 +5660,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="571363680"/>
+        <c:crossAx val="-649870736"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -11277,52 +11283,52 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:9" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
     </row>
     <row r="6" spans="3:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="15"/>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="3:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="15"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" spans="3:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="20" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="3">
@@ -11345,7 +11351,7 @@
       </c>
     </row>
     <row r="9" spans="3:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="14"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="3">
         <v>4</v>
       </c>
@@ -11366,7 +11372,7 @@
       </c>
     </row>
     <row r="10" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="14"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="3">
         <v>5</v>
       </c>
@@ -11387,7 +11393,7 @@
       </c>
     </row>
     <row r="11" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="14"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="3">
         <v>4</v>
       </c>
@@ -11408,7 +11414,7 @@
       </c>
     </row>
     <row r="12" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="14"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="3">
         <v>4</v>
       </c>
@@ -11429,7 +11435,7 @@
       </c>
     </row>
     <row r="13" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="14"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="3">
         <v>5</v>
       </c>
@@ -11450,7 +11456,7 @@
       </c>
     </row>
     <row r="14" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="3">
@@ -11473,7 +11479,7 @@
       </c>
     </row>
     <row r="15" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C15" s="14"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="3">
         <v>4</v>
       </c>
@@ -11494,7 +11500,7 @@
       </c>
     </row>
     <row r="16" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C16" s="14"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="3">
         <v>6</v>
       </c>
@@ -11515,7 +11521,7 @@
       </c>
     </row>
     <row r="17" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C17" s="14"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="3">
         <v>5</v>
       </c>
@@ -11536,7 +11542,7 @@
       </c>
     </row>
     <row r="18" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C18" s="14"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="3">
         <v>4</v>
       </c>
@@ -11557,7 +11563,7 @@
       </c>
     </row>
     <row r="19" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C19" s="14"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="3">
         <v>4</v>
       </c>
@@ -11578,7 +11584,7 @@
       </c>
     </row>
     <row r="20" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="20" t="s">
         <v>0</v>
       </c>
       <c r="D20" s="3">
@@ -11601,7 +11607,7 @@
       </c>
     </row>
     <row r="21" spans="3:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="14"/>
+      <c r="C21" s="20"/>
       <c r="D21" s="3">
         <v>4</v>
       </c>
@@ -11622,7 +11628,7 @@
       </c>
     </row>
     <row r="22" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="14"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="3">
         <v>5</v>
       </c>
@@ -11643,7 +11649,7 @@
       </c>
     </row>
     <row r="23" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="14"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="3">
         <v>4</v>
       </c>
@@ -11664,7 +11670,7 @@
       </c>
     </row>
     <row r="24" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="14"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="3">
         <v>4</v>
       </c>
@@ -11685,7 +11691,7 @@
       </c>
     </row>
     <row r="25" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="14"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="3">
         <v>5</v>
       </c>
@@ -11706,7 +11712,7 @@
       </c>
     </row>
     <row r="26" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D26" s="3">
@@ -11729,7 +11735,7 @@
       </c>
     </row>
     <row r="27" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C27" s="14"/>
+      <c r="C27" s="20"/>
       <c r="D27" s="3">
         <v>4</v>
       </c>
@@ -11750,7 +11756,7 @@
       </c>
     </row>
     <row r="28" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C28" s="14"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="3">
         <v>6</v>
       </c>
@@ -11771,7 +11777,7 @@
       </c>
     </row>
     <row r="29" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C29" s="14"/>
+      <c r="C29" s="20"/>
       <c r="D29" s="3">
         <v>5</v>
       </c>
@@ -11792,7 +11798,7 @@
       </c>
     </row>
     <row r="30" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C30" s="14"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="3">
         <v>4</v>
       </c>
@@ -11813,7 +11819,7 @@
       </c>
     </row>
     <row r="31" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C31" s="14"/>
+      <c r="C31" s="20"/>
       <c r="D31" s="3">
         <v>4</v>
       </c>
@@ -11835,11 +11841,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
@@ -11848,6 +11849,11 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="I6:I7"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="C20:C25"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11870,19 +11876,19 @@
       <c r="F11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14" t="s">
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
     </row>
     <row r="12" spans="6:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="23" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -11905,7 +11911,7 @@
       </c>
     </row>
     <row r="13" spans="6:12" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F13" s="17"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="4">
         <v>0.159</v>
       </c>
@@ -12182,16 +12188,16 @@
       <c r="D6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D7" s="8"/>
@@ -12330,90 +12336,90 @@
   </cols>
   <sheetData>
     <row r="8" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="16">
         <v>3.4</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="16">
         <v>3.38</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="16">
         <v>3.39</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="16">
         <v>3.37</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="16">
         <v>3.45</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="16">
         <v>3.41</v>
       </c>
     </row>
     <row r="12" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="16">
         <v>3.41</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="16">
         <v>3.39</v>
       </c>
     </row>
     <row r="13" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D13" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="22">
+      <c r="D13" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="16">
         <v>3.4</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="16">
         <v>3.37</v>
       </c>
     </row>
-    <row r="14" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D14" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="22">
+    <row r="14" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="D14" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="16">
         <v>3.42</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="16">
         <v>3.39</v>
       </c>
     </row>
     <row r="15" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D15" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="20">
+      <c r="D15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="14">
         <v>3.41</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="14">
         <v>3.38</v>
       </c>
     </row>
@@ -12430,95 +12436,95 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" style="25" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="25" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" style="19" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="18">
         <v>3.46</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="18">
         <v>3.41</v>
       </c>
     </row>
     <row r="6" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="18">
         <v>3.44</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="18">
         <v>3.4</v>
       </c>
     </row>
     <row r="7" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="18">
         <v>3.54</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="18">
         <v>3.47</v>
       </c>
     </row>
     <row r="8" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="18">
         <v>3.49</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="18">
         <v>3.44</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="24">
+      <c r="D9" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E9" s="18">
         <v>3.47</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18">
         <v>3.42</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="24">
+      <c r="D10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="18">
         <v>3.48</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <v>3.43</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="19">
+      <c r="D11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="13">
         <v>3.48</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="13">
         <v>3.42</v>
       </c>
     </row>
@@ -12539,90 +12545,90 @@
   </cols>
   <sheetData>
     <row r="7" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="18">
         <v>3.27</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="18">
         <v>3.2</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="18">
         <v>3.25</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18">
         <v>3.18</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="18">
         <v>3.36</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <v>3.27</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="18">
         <v>3.3</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="18">
         <v>3.22</v>
       </c>
     </row>
-    <row r="12" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D12" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="24">
+    <row r="12" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D12" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="18">
         <v>3.28</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="18">
         <v>3.19</v>
       </c>
     </row>
-    <row r="13" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D13" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="24">
+    <row r="13" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D13" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="18">
         <v>3.29</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="18">
         <v>3.21</v>
       </c>
     </row>
     <row r="14" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="19">
+      <c r="D14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="13">
         <v>3.29</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="13">
         <v>3.21</v>
       </c>
     </row>
@@ -12643,90 +12649,90 @@
   </cols>
   <sheetData>
     <row r="6" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>32</v>
+      <c r="E6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="18">
         <v>3.34</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="18">
         <v>3.3</v>
       </c>
     </row>
     <row r="8" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="18">
         <v>3.33</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="18">
         <v>3.28</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="18">
         <v>3.42</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18">
         <v>3.35</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="18">
         <v>3.37</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <v>3.32</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="24">
+      <c r="D11" s="18" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" s="18">
         <v>3.35</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="18">
         <v>3.3</v>
       </c>
     </row>
-    <row r="12" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D12" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="24">
+    <row r="12" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="D12" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="18">
         <v>3.36</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="18">
         <v>3.31</v>
       </c>
     </row>
     <row r="13" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D13" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="19">
+      <c r="D13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="13">
         <v>3.36</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="13">
         <v>3.31</v>
       </c>
     </row>
@@ -12742,234 +12748,234 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="7" spans="4:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="H7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="I7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="J7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="K7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="L7" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="4:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="15">
         <v>3.4</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="15">
         <v>3.38</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="15">
         <v>3.46</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="15">
         <v>3.41</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="15">
         <v>3.27</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="15">
         <v>3.2</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="15">
         <v>3.34</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="15">
         <v>3.3</v>
       </c>
     </row>
     <row r="9" spans="4:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="15">
         <v>3.39</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="15">
         <v>3.37</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="15">
         <v>3.44</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="15">
         <v>3.4</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="15">
         <v>3.25</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="15">
         <v>3.18</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="15">
         <v>3.33</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="15">
         <v>3.28</v>
       </c>
     </row>
     <row r="10" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="15">
         <v>3.45</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="15">
         <v>3.41</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="15">
         <v>3.54</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="15">
         <v>3.47</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="15">
         <v>3.36</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="15">
         <v>3.27</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="15">
         <v>3.42</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="15">
         <v>3.35</v>
       </c>
     </row>
     <row r="11" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="15">
         <v>3.41</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="15">
         <v>3.39</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="15">
         <v>3.49</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="15">
         <v>3.44</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="15">
         <v>3.3</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="15">
         <v>3.22</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="15">
         <v>3.37</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="15">
         <v>3.32</v>
       </c>
     </row>
-    <row r="12" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D12" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="21">
+    <row r="12" spans="4:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="D12" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="E12" s="15">
         <v>3.4</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="15">
         <v>3.37</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="15">
         <v>3.47</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="15">
         <v>3.42</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="15">
         <v>3.28</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="15">
         <v>3.19</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="15">
         <v>3.35</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="15">
         <v>3.3</v>
       </c>
     </row>
-    <row r="13" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="21">
+    <row r="13" spans="4:12" ht="46.8" x14ac:dyDescent="0.3">
+      <c r="D13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="15">
         <v>3.42</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="15">
         <v>3.39</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="15">
         <v>3.48</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="15">
         <v>3.43</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="15">
         <v>3.29</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="15">
         <v>3.21</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="15">
         <v>3.36</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="15">
         <v>3.31</v>
       </c>
     </row>
     <row r="14" spans="4:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D14" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="23">
+      <c r="D14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="17">
         <v>3.41</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="17">
         <v>3.38</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="17">
         <v>3.48</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="17">
         <v>3.42</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="17">
         <v>3.29</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="17">
         <v>3.21</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="17">
         <v>3.36</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="17">
         <v>3.31</v>
       </c>
     </row>

--- a/Книга1.xlsx
+++ b/Книга1.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\GitHub\nurmatova_nargiza\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OSPanel\home\nurmatova_nargiza\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" activeTab="8"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="9264" firstSheet="4" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="Лист2" sheetId="2" r:id="rId1"/>
@@ -23,7 +23,6 @@
     <sheet name="Лист9" sheetId="10" r:id="rId9"/>
   </sheets>
   <calcPr calcId="152511"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -119,12 +118,6 @@
     <t>Toshkent 319-son</t>
   </si>
   <si>
-    <t>Jizzax 45-son</t>
-  </si>
-  <si>
-    <t>Jizzax 125-son</t>
-  </si>
-  <si>
     <t>Jami</t>
   </si>
   <si>
@@ -160,11 +153,17 @@
   <si>
     <t>R (NG)</t>
   </si>
+  <si>
+    <t>Namangan 45-son</t>
+  </si>
+  <si>
+    <t>Namangan 125-son</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -298,24 +297,6 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -337,6 +318,24 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" textRotation="90" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
@@ -355,7 +354,7 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -435,6 +434,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B01A-4A4F-9A30-7BF82FD761C0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -496,6 +500,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-B01A-4A4F-9A30-7BF82FD761C0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -557,6 +566,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B01A-4A4F-9A30-7BF82FD761C0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -618,6 +632,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-B01A-4A4F-9A30-7BF82FD761C0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -679,6 +698,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-B01A-4A4F-9A30-7BF82FD761C0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
@@ -740,6 +764,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-B01A-4A4F-9A30-7BF82FD761C0}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -795,7 +824,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="305485328"/>
@@ -854,7 +883,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="305484784"/>
@@ -895,7 +924,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -907,7 +936,7 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -921,6 +950,7 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -946,7 +976,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -1008,7 +1038,7 @@
                     <a:cs typeface="+mn-cs"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -1021,6 +1051,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1102,6 +1133,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-A872-4354-9AEC-85FEDCE292A6}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="outEnd"/>
@@ -1158,7 +1194,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="305492400"/>
@@ -1217,7 +1253,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="305490224"/>
@@ -1258,7 +1294,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -1270,7 +1306,7 @@
 </file>
 
 <file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -1339,7 +1375,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -1352,6 +1388,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1463,6 +1500,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1B32-443C-99BB-A135722420F9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -1519,7 +1561,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -1532,6 +1574,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1643,6 +1686,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1B32-443C-99BB-A135722420F9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -1693,7 +1741,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -1706,6 +1754,7 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
+                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -1817,6 +1866,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1B32-443C-99BB-A135722420F9}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="outEnd"/>
@@ -1870,7 +1924,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="354215728"/>
@@ -1929,7 +1983,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="354208112"/>
@@ -1946,6 +2000,7 @@
     </c:plotArea>
     <c:legend>
       <c:legendPos val="b"/>
+      <c:layout/>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -1971,7 +2026,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2010,7 +2065,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2022,7 +2077,7 @@
 </file>
 
 <file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -2062,7 +2117,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:title>
@@ -2160,6 +2215,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-39B8-4527-BFFC-621CD569B60A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2248,6 +2308,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-39B8-4527-BFFC-621CD569B60A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -2336,6 +2401,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-39B8-4527-BFFC-621CD569B60A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -2424,6 +2494,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-39B8-4527-BFFC-621CD569B60A}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -2479,7 +2554,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="354218992"/>
@@ -2538,7 +2613,7 @@
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="354209200"/>
@@ -2581,7 +2656,7 @@
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -2611,7 +2686,7 @@
       <a:pPr>
         <a:defRPr/>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -2623,7 +2698,7 @@
 </file>
 
 <file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -2694,6 +2769,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000000-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2714,6 +2792,9 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000001-8F38-48F5-98CF-53CC37426030}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2736,6 +2817,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000002-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2756,6 +2840,9 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000003-8F38-48F5-98CF-53CC37426030}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2778,6 +2865,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000004-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2799,6 +2889,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000005-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -2819,6 +2912,9 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000006-8F38-48F5-98CF-53CC37426030}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -2843,7 +2939,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="inEnd"/>
@@ -2856,7 +2952,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -2892,10 +2987,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -2933,6 +3028,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000007-8F38-48F5-98CF-53CC37426030}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -2985,6 +3085,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000008-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -3005,6 +3108,9 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{00000009-8F38-48F5-98CF-53CC37426030}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3027,6 +3133,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000A-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -3047,6 +3156,9 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000B-8F38-48F5-98CF-53CC37426030}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3069,6 +3181,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000C-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -3090,6 +3205,9 @@
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
                 </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000D-8F38-48F5-98CF-53CC37426030}"/>
+                </c:ext>
               </c:extLst>
             </c:dLbl>
             <c:dLbl>
@@ -3110,6 +3228,9 @@
               <c:extLst>
                 <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
                   <c15:layout/>
+                </c:ext>
+                <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                  <c16:uniqueId val="{0000000E-8F38-48F5-98CF-53CC37426030}"/>
                 </c:ext>
               </c:extLst>
             </c:dLbl>
@@ -3134,7 +3255,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="inEnd"/>
@@ -3147,7 +3268,6 @@
             <c:showLeaderLines val="0"/>
             <c:extLst>
               <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}">
-                <c15:layout/>
                 <c15:showLeaderLines val="1"/>
                 <c15:leaderLines>
                   <c:spPr>
@@ -3183,10 +3303,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -3224,6 +3344,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{0000000F-8F38-48F5-98CF-53CC37426030}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="inEnd"/>
@@ -3276,7 +3401,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="357946400"/>
@@ -3365,7 +3490,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3396,7 +3521,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3408,7 +3533,7 @@
 </file>
 
 <file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -3474,7 +3599,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -3524,10 +3649,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -3565,6 +3690,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-F36E-42E2-928D-E772E53FA6AD}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -3612,7 +3742,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -3662,10 +3792,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -3703,6 +3833,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-F36E-42E2-928D-E772E53FA6AD}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="outEnd"/>
@@ -3756,7 +3891,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="565840160"/>
@@ -3812,7 +3947,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="565837984"/>
@@ -3852,7 +3987,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -3888,7 +4023,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -3900,7 +4035,7 @@
 </file>
 
 <file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -3968,7 +4103,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -4018,10 +4153,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4059,6 +4194,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1098-4F1C-87AA-78C6BE2DD4C2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -4108,7 +4248,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -4158,10 +4298,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4199,6 +4339,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1098-4F1C-87AA-78C6BE2DD4C2}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="outEnd"/>
@@ -4252,7 +4397,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="571364768"/>
@@ -4308,7 +4453,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="571369664"/>
@@ -4348,7 +4493,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4384,7 +4529,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4396,7 +4541,7 @@
 </file>
 
 <file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -4464,7 +4609,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -4514,10 +4659,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4555,6 +4700,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-167C-4DC2-BC36-708DF3227B8C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -4604,7 +4754,7 @@
                     <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                   </a:defRPr>
                 </a:pPr>
-                <a:endParaRPr lang="en-US"/>
+                <a:endParaRPr lang="ru-RU"/>
               </a:p>
             </c:txPr>
             <c:dLblPos val="outEnd"/>
@@ -4654,10 +4804,10 @@
                   <c:v>Toshkent 319-son</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
                 <c:pt idx="6">
                   <c:v>Jami</c:v>
@@ -4695,6 +4845,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-167C-4DC2-BC36-708DF3227B8C}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:dLblPos val="outEnd"/>
@@ -4748,7 +4903,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="565168080"/>
@@ -4804,7 +4959,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="565167536"/>
@@ -4844,7 +4999,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -4880,7 +5035,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -4892,7 +5047,7 @@
 </file>
 
 <file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ru-RU"/>
   <c:roundedCorners val="0"/>
@@ -5001,6 +5156,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-98D3-4199-B5A1-D684D289A19E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="1"/>
@@ -5091,6 +5251,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-98D3-4199-B5A1-D684D289A19E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="2"/>
@@ -5181,6 +5346,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-98D3-4199-B5A1-D684D289A19E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="3"/>
@@ -5271,6 +5441,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-98D3-4199-B5A1-D684D289A19E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="4"/>
@@ -5281,7 +5456,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jizzax 45-son</c:v>
+                  <c:v>Namangan 45-son</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5361,6 +5536,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-98D3-4199-B5A1-D684D289A19E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="5"/>
@@ -5371,7 +5551,7 @@
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Jizzax 125-son</c:v>
+                  <c:v>Namangan 125-son</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -5451,6 +5631,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-98D3-4199-B5A1-D684D289A19E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:ser>
           <c:idx val="6"/>
@@ -5543,6 +5728,11 @@
               </c:numCache>
             </c:numRef>
           </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-98D3-4199-B5A1-D684D289A19E}"/>
+            </c:ext>
+          </c:extLst>
         </c:ser>
         <c:dLbls>
           <c:showLegendKey val="0"/>
@@ -5595,7 +5785,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="571370752"/>
@@ -5651,7 +5841,7 @@
                 <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
-            <a:endParaRPr lang="en-US"/>
+            <a:endParaRPr lang="ru-RU"/>
           </a:p>
         </c:txPr>
         <c:crossAx val="571363680"/>
@@ -5691,7 +5881,7 @@
               <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
-          <a:endParaRPr lang="en-US"/>
+          <a:endParaRPr lang="ru-RU"/>
         </a:p>
       </c:txPr>
     </c:legend>
@@ -5727,7 +5917,7 @@
           <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
         </a:defRPr>
       </a:pPr>
-      <a:endParaRPr lang="en-US"/>
+      <a:endParaRPr lang="ru-RU"/>
     </a:p>
   </c:txPr>
   <c:printSettings>
@@ -11277,52 +11467,52 @@
   </cols>
   <sheetData>
     <row r="5" spans="3:9" ht="51.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D5" s="14" t="s">
+      <c r="D5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14"/>
-      <c r="G5" s="14" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20"/>
+      <c r="G5" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
     </row>
     <row r="6" spans="3:9" ht="25.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C6" s="15"/>
-      <c r="D6" s="13" t="s">
+      <c r="C6" s="22"/>
+      <c r="D6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="E6" s="13" t="s">
+      <c r="E6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="G6" s="13" t="s">
+      <c r="G6" s="21" t="s">
         <v>5</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="21" t="s">
         <v>6</v>
       </c>
-      <c r="I6" s="13" t="s">
+      <c r="I6" s="21" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="7" spans="3:9" ht="28.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C7" s="15"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="21"/>
+      <c r="E7" s="21"/>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" spans="3:9" ht="19.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="20" t="s">
         <v>0</v>
       </c>
       <c r="D8" s="3">
@@ -11345,7 +11535,7 @@
       </c>
     </row>
     <row r="9" spans="3:9" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C9" s="14"/>
+      <c r="C9" s="20"/>
       <c r="D9" s="3">
         <v>4</v>
       </c>
@@ -11366,7 +11556,7 @@
       </c>
     </row>
     <row r="10" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C10" s="14"/>
+      <c r="C10" s="20"/>
       <c r="D10" s="3">
         <v>5</v>
       </c>
@@ -11387,7 +11577,7 @@
       </c>
     </row>
     <row r="11" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="14"/>
+      <c r="C11" s="20"/>
       <c r="D11" s="3">
         <v>4</v>
       </c>
@@ -11408,7 +11598,7 @@
       </c>
     </row>
     <row r="12" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C12" s="14"/>
+      <c r="C12" s="20"/>
       <c r="D12" s="3">
         <v>4</v>
       </c>
@@ -11429,7 +11619,7 @@
       </c>
     </row>
     <row r="13" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C13" s="14"/>
+      <c r="C13" s="20"/>
       <c r="D13" s="3">
         <v>5</v>
       </c>
@@ -11450,7 +11640,7 @@
       </c>
     </row>
     <row r="14" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C14" s="14" t="s">
+      <c r="C14" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D14" s="3">
@@ -11473,7 +11663,7 @@
       </c>
     </row>
     <row r="15" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C15" s="14"/>
+      <c r="C15" s="20"/>
       <c r="D15" s="3">
         <v>4</v>
       </c>
@@ -11494,7 +11684,7 @@
       </c>
     </row>
     <row r="16" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C16" s="14"/>
+      <c r="C16" s="20"/>
       <c r="D16" s="3">
         <v>6</v>
       </c>
@@ -11515,7 +11705,7 @@
       </c>
     </row>
     <row r="17" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C17" s="14"/>
+      <c r="C17" s="20"/>
       <c r="D17" s="3">
         <v>5</v>
       </c>
@@ -11536,7 +11726,7 @@
       </c>
     </row>
     <row r="18" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C18" s="14"/>
+      <c r="C18" s="20"/>
       <c r="D18" s="3">
         <v>4</v>
       </c>
@@ -11557,7 +11747,7 @@
       </c>
     </row>
     <row r="19" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C19" s="14"/>
+      <c r="C19" s="20"/>
       <c r="D19" s="3">
         <v>4</v>
       </c>
@@ -11578,7 +11768,7 @@
       </c>
     </row>
     <row r="20" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="20" t="s">
         <v>0</v>
       </c>
       <c r="D20" s="3">
@@ -11601,7 +11791,7 @@
       </c>
     </row>
     <row r="21" spans="3:9" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C21" s="14"/>
+      <c r="C21" s="20"/>
       <c r="D21" s="3">
         <v>4</v>
       </c>
@@ -11622,7 +11812,7 @@
       </c>
     </row>
     <row r="22" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C22" s="14"/>
+      <c r="C22" s="20"/>
       <c r="D22" s="3">
         <v>5</v>
       </c>
@@ -11643,7 +11833,7 @@
       </c>
     </row>
     <row r="23" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C23" s="14"/>
+      <c r="C23" s="20"/>
       <c r="D23" s="3">
         <v>4</v>
       </c>
@@ -11664,7 +11854,7 @@
       </c>
     </row>
     <row r="24" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C24" s="14"/>
+      <c r="C24" s="20"/>
       <c r="D24" s="3">
         <v>4</v>
       </c>
@@ -11685,7 +11875,7 @@
       </c>
     </row>
     <row r="25" spans="3:9" ht="16.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C25" s="14"/>
+      <c r="C25" s="20"/>
       <c r="D25" s="3">
         <v>5</v>
       </c>
@@ -11706,7 +11896,7 @@
       </c>
     </row>
     <row r="26" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C26" s="14" t="s">
+      <c r="C26" s="20" t="s">
         <v>1</v>
       </c>
       <c r="D26" s="3">
@@ -11729,7 +11919,7 @@
       </c>
     </row>
     <row r="27" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C27" s="14"/>
+      <c r="C27" s="20"/>
       <c r="D27" s="3">
         <v>4</v>
       </c>
@@ -11750,7 +11940,7 @@
       </c>
     </row>
     <row r="28" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C28" s="14"/>
+      <c r="C28" s="20"/>
       <c r="D28" s="3">
         <v>6</v>
       </c>
@@ -11771,7 +11961,7 @@
       </c>
     </row>
     <row r="29" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C29" s="14"/>
+      <c r="C29" s="20"/>
       <c r="D29" s="3">
         <v>5</v>
       </c>
@@ -11792,7 +11982,7 @@
       </c>
     </row>
     <row r="30" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C30" s="14"/>
+      <c r="C30" s="20"/>
       <c r="D30" s="3">
         <v>4</v>
       </c>
@@ -11813,7 +12003,7 @@
       </c>
     </row>
     <row r="31" spans="3:9" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="C31" s="14"/>
+      <c r="C31" s="20"/>
       <c r="D31" s="3">
         <v>4</v>
       </c>
@@ -11835,11 +12025,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="C26:C31"/>
-    <mergeCell ref="C20:C25"/>
-    <mergeCell ref="C14:C19"/>
-    <mergeCell ref="D6:D7"/>
-    <mergeCell ref="E6:E7"/>
     <mergeCell ref="F6:F7"/>
     <mergeCell ref="G6:G7"/>
     <mergeCell ref="H6:H7"/>
@@ -11848,6 +12033,11 @@
     <mergeCell ref="D5:F5"/>
     <mergeCell ref="G5:I5"/>
     <mergeCell ref="I6:I7"/>
+    <mergeCell ref="C26:C31"/>
+    <mergeCell ref="C20:C25"/>
+    <mergeCell ref="C14:C19"/>
+    <mergeCell ref="D6:D7"/>
+    <mergeCell ref="E6:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -11870,19 +12060,19 @@
       <c r="F11" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14" t="s">
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20" t="s">
         <v>3</v>
       </c>
-      <c r="K11" s="14"/>
-      <c r="L11" s="14"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="20"/>
     </row>
     <row r="12" spans="6:12" ht="31.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="23" t="s">
         <v>0</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -11905,7 +12095,7 @@
       </c>
     </row>
     <row r="13" spans="6:12" ht="34.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="F13" s="17"/>
+      <c r="F13" s="24"/>
       <c r="G13" s="4">
         <v>0.159</v>
       </c>
@@ -12182,16 +12372,16 @@
       <c r="D6" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="E6" s="18" t="s">
+      <c r="E6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18" t="s">
+      <c r="F6" s="25"/>
+      <c r="G6" s="25"/>
+      <c r="H6" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="I6" s="18"/>
-      <c r="J6" s="18"/>
+      <c r="I6" s="25"/>
+      <c r="J6" s="25"/>
     </row>
     <row r="7" spans="4:10" x14ac:dyDescent="0.3">
       <c r="D7" s="8"/>
@@ -12330,90 +12520,90 @@
   </cols>
   <sheetData>
     <row r="8" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D8" s="19" t="s">
+      <c r="D8" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="19" t="s">
+      <c r="E8" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="F8" s="19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="22">
+      <c r="E9" s="16">
         <v>3.4</v>
       </c>
-      <c r="F9" s="22">
+      <c r="F9" s="16">
         <v>3.38</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E10" s="22">
+      <c r="E10" s="16">
         <v>3.39</v>
       </c>
-      <c r="F10" s="22">
+      <c r="F10" s="16">
         <v>3.37</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E11" s="22">
+      <c r="E11" s="16">
         <v>3.45</v>
       </c>
-      <c r="F11" s="22">
+      <c r="F11" s="16">
         <v>3.41</v>
       </c>
     </row>
     <row r="12" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="16">
         <v>3.41</v>
       </c>
-      <c r="F12" s="22">
+      <c r="F12" s="16">
         <v>3.39</v>
       </c>
     </row>
     <row r="13" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D13" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E13" s="22">
+      <c r="D13" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E13" s="16">
         <v>3.4</v>
       </c>
-      <c r="F13" s="22">
+      <c r="F13" s="16">
         <v>3.37</v>
       </c>
     </row>
     <row r="14" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D14" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E14" s="22">
+      <c r="D14" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E14" s="16">
         <v>3.42</v>
       </c>
-      <c r="F14" s="22">
+      <c r="F14" s="16">
         <v>3.39</v>
       </c>
     </row>
     <row r="15" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D15" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E15" s="20">
+      <c r="D15" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E15" s="14">
         <v>3.41</v>
       </c>
-      <c r="F15" s="20">
+      <c r="F15" s="14">
         <v>3.38</v>
       </c>
     </row>
@@ -12430,95 +12620,95 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" style="25" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="25" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" style="19" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="19" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="4" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F4" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="F4" s="19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="5" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E5" s="24">
+      <c r="E5" s="18">
         <v>3.46</v>
       </c>
-      <c r="F5" s="24">
+      <c r="F5" s="18">
         <v>3.41</v>
       </c>
     </row>
     <row r="6" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D6" s="21" t="s">
+      <c r="D6" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E6" s="24">
+      <c r="E6" s="18">
         <v>3.44</v>
       </c>
-      <c r="F6" s="24">
+      <c r="F6" s="18">
         <v>3.4</v>
       </c>
     </row>
     <row r="7" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D7" s="21" t="s">
+      <c r="D7" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="18">
         <v>3.54</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="18">
         <v>3.47</v>
       </c>
     </row>
     <row r="8" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="18">
         <v>3.49</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="18">
         <v>3.44</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D9" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E9" s="24">
+      <c r="D9" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E9" s="18">
         <v>3.47</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18">
         <v>3.42</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="24">
+      <c r="D10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="18">
         <v>3.48</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <v>3.43</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E11" s="19">
+      <c r="D11" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E11" s="13">
         <v>3.48</v>
       </c>
-      <c r="F11" s="19">
+      <c r="F11" s="13">
         <v>3.42</v>
       </c>
     </row>
@@ -12539,90 +12729,90 @@
   </cols>
   <sheetData>
     <row r="7" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F7" s="13" t="s">
         <v>31</v>
-      </c>
-      <c r="F7" s="19" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="8" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="18">
         <v>3.27</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="18">
         <v>3.2</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="18">
         <v>3.25</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18">
         <v>3.18</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="18">
         <v>3.36</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <v>3.27</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="24">
+      <c r="E11" s="18">
         <v>3.3</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="18">
         <v>3.22</v>
       </c>
     </row>
     <row r="12" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D12" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="24">
+      <c r="D12" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="18">
         <v>3.28</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="18">
         <v>3.19</v>
       </c>
     </row>
     <row r="13" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D13" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="24">
+      <c r="D13" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="18">
         <v>3.29</v>
       </c>
-      <c r="F13" s="24">
+      <c r="F13" s="18">
         <v>3.21</v>
       </c>
     </row>
     <row r="14" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D14" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="19">
+      <c r="D14" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="13">
         <v>3.29</v>
       </c>
-      <c r="F14" s="19">
+      <c r="F14" s="13">
         <v>3.21</v>
       </c>
     </row>
@@ -12643,90 +12833,90 @@
   </cols>
   <sheetData>
     <row r="6" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E6" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="F6" s="19" t="s">
-        <v>32</v>
+      <c r="E6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D7" s="24" t="s">
+      <c r="D7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="24">
+      <c r="E7" s="18">
         <v>3.34</v>
       </c>
-      <c r="F7" s="24">
+      <c r="F7" s="18">
         <v>3.3</v>
       </c>
     </row>
     <row r="8" spans="4:6" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D8" s="24" t="s">
+      <c r="D8" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="24">
+      <c r="E8" s="18">
         <v>3.33</v>
       </c>
-      <c r="F8" s="24">
+      <c r="F8" s="18">
         <v>3.28</v>
       </c>
     </row>
     <row r="9" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="18" t="s">
         <v>26</v>
       </c>
-      <c r="E9" s="24">
+      <c r="E9" s="18">
         <v>3.42</v>
       </c>
-      <c r="F9" s="24">
+      <c r="F9" s="18">
         <v>3.35</v>
       </c>
     </row>
     <row r="10" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D10" s="24" t="s">
+      <c r="D10" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="24">
+      <c r="E10" s="18">
         <v>3.37</v>
       </c>
-      <c r="F10" s="24">
+      <c r="F10" s="18">
         <v>3.32</v>
       </c>
     </row>
     <row r="11" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D11" s="24" t="s">
-        <v>28</v>
-      </c>
-      <c r="E11" s="24">
+      <c r="D11" s="18" t="s">
+        <v>40</v>
+      </c>
+      <c r="E11" s="18">
         <v>3.35</v>
       </c>
-      <c r="F11" s="24">
+      <c r="F11" s="18">
         <v>3.3</v>
       </c>
     </row>
     <row r="12" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D12" s="24" t="s">
-        <v>29</v>
-      </c>
-      <c r="E12" s="24">
+      <c r="D12" s="18" t="s">
+        <v>41</v>
+      </c>
+      <c r="E12" s="18">
         <v>3.36</v>
       </c>
-      <c r="F12" s="24">
+      <c r="F12" s="18">
         <v>3.31</v>
       </c>
     </row>
     <row r="13" spans="4:6" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D13" s="19" t="s">
-        <v>30</v>
-      </c>
-      <c r="E13" s="19">
+      <c r="D13" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="E13" s="13">
         <v>3.36</v>
       </c>
-      <c r="F13" s="19">
+      <c r="F13" s="13">
         <v>3.31</v>
       </c>
     </row>
@@ -12742,234 +12932,234 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="7" spans="4:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="G7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="H7" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="I7" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="J7" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="K7" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="L7" s="13" t="s">
         <v>39</v>
-      </c>
-      <c r="K7" s="19" t="s">
-        <v>40</v>
-      </c>
-      <c r="L7" s="19" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="8" spans="4:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="15">
         <v>3.4</v>
       </c>
-      <c r="F8" s="21">
+      <c r="F8" s="15">
         <v>3.38</v>
       </c>
-      <c r="G8" s="21">
+      <c r="G8" s="15">
         <v>3.46</v>
       </c>
-      <c r="H8" s="21">
+      <c r="H8" s="15">
         <v>3.41</v>
       </c>
-      <c r="I8" s="21">
+      <c r="I8" s="15">
         <v>3.27</v>
       </c>
-      <c r="J8" s="21">
+      <c r="J8" s="15">
         <v>3.2</v>
       </c>
-      <c r="K8" s="21">
+      <c r="K8" s="15">
         <v>3.34</v>
       </c>
-      <c r="L8" s="21">
+      <c r="L8" s="15">
         <v>3.3</v>
       </c>
     </row>
     <row r="9" spans="4:12" ht="46.8" x14ac:dyDescent="0.3">
-      <c r="D9" s="21" t="s">
+      <c r="D9" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E9" s="15">
         <v>3.39</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F9" s="15">
         <v>3.37</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G9" s="15">
         <v>3.44</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H9" s="15">
         <v>3.4</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I9" s="15">
         <v>3.25</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J9" s="15">
         <v>3.18</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K9" s="15">
         <v>3.33</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L9" s="15">
         <v>3.28</v>
       </c>
     </row>
     <row r="10" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E10" s="15">
         <v>3.45</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F10" s="15">
         <v>3.41</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G10" s="15">
         <v>3.54</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H10" s="15">
         <v>3.47</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I10" s="15">
         <v>3.36</v>
       </c>
-      <c r="J10" s="21">
+      <c r="J10" s="15">
         <v>3.27</v>
       </c>
-      <c r="K10" s="21">
+      <c r="K10" s="15">
         <v>3.42</v>
       </c>
-      <c r="L10" s="21">
+      <c r="L10" s="15">
         <v>3.35</v>
       </c>
     </row>
     <row r="11" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D11" s="21" t="s">
+      <c r="D11" s="15" t="s">
         <v>27</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E11" s="15">
         <v>3.41</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F11" s="15">
         <v>3.39</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G11" s="15">
         <v>3.49</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H11" s="15">
         <v>3.44</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I11" s="15">
         <v>3.3</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="15">
         <v>3.22</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K11" s="15">
         <v>3.37</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L11" s="15">
         <v>3.32</v>
       </c>
     </row>
     <row r="12" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D12" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="E12" s="21">
+      <c r="D12" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="E12" s="15">
         <v>3.4</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="15">
         <v>3.37</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G12" s="15">
         <v>3.47</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H12" s="15">
         <v>3.42</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I12" s="15">
         <v>3.28</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="15">
         <v>3.19</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K12" s="15">
         <v>3.35</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L12" s="15">
         <v>3.3</v>
       </c>
     </row>
     <row r="13" spans="4:12" ht="31.2" x14ac:dyDescent="0.3">
-      <c r="D13" s="21" t="s">
-        <v>29</v>
-      </c>
-      <c r="E13" s="21">
+      <c r="D13" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="E13" s="15">
         <v>3.42</v>
       </c>
-      <c r="F13" s="21">
+      <c r="F13" s="15">
         <v>3.39</v>
       </c>
-      <c r="G13" s="21">
+      <c r="G13" s="15">
         <v>3.48</v>
       </c>
-      <c r="H13" s="21">
+      <c r="H13" s="15">
         <v>3.43</v>
       </c>
-      <c r="I13" s="21">
+      <c r="I13" s="15">
         <v>3.29</v>
       </c>
-      <c r="J13" s="21">
+      <c r="J13" s="15">
         <v>3.21</v>
       </c>
-      <c r="K13" s="21">
+      <c r="K13" s="15">
         <v>3.36</v>
       </c>
-      <c r="L13" s="21">
+      <c r="L13" s="15">
         <v>3.31</v>
       </c>
     </row>
     <row r="14" spans="4:12" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="D14" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="E14" s="23">
+      <c r="D14" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="E14" s="17">
         <v>3.41</v>
       </c>
-      <c r="F14" s="23">
+      <c r="F14" s="17">
         <v>3.38</v>
       </c>
-      <c r="G14" s="23">
+      <c r="G14" s="17">
         <v>3.48</v>
       </c>
-      <c r="H14" s="23">
+      <c r="H14" s="17">
         <v>3.42</v>
       </c>
-      <c r="I14" s="23">
+      <c r="I14" s="17">
         <v>3.29</v>
       </c>
-      <c r="J14" s="23">
+      <c r="J14" s="17">
         <v>3.21</v>
       </c>
-      <c r="K14" s="23">
+      <c r="K14" s="17">
         <v>3.36</v>
       </c>
-      <c r="L14" s="23">
+      <c r="L14" s="17">
         <v>3.31</v>
       </c>
     </row>
